--- a/Compititor's_Price/Unilin_Prices/Unilin_Prices_11-02-2026.xlsx
+++ b/Compititor's_Price/Unilin_Prices/Unilin_Prices_11-02-2026.xlsx
@@ -1593,12 +1593,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>£40.69</t>
+          <t>£40.49</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>£40.69</t>
+          <t>£40.49</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
